--- a/AdditionalData/Tables/Cumulative Height per Turn for Different Ramp Angles ext.xlsx
+++ b/AdditionalData/Tables/Cumulative Height per Turn for Different Ramp Angles ext.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="deepseek_csv_20251016_59ab78" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -865,6 +865,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -924,8 +925,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1055,920 +1060,920 @@
   <dimension ref="A1:AA11"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="2" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="2" style="1" width="7"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="0" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="0" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="0" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="0" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="0" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="0" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="0" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="0" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="0" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="0" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="M2" s="0" t="s">
+      <c r="M2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N2" s="0" t="s">
+      <c r="N2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O2" s="0" t="s">
+      <c r="O2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P2" s="0" t="s">
+      <c r="P2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="0" t="s">
+      <c r="Q2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="R2" s="0" t="s">
+      <c r="R2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="S2" s="0" t="s">
+      <c r="S2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="T2" s="0" t="s">
+      <c r="T2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="U2" s="0" t="s">
+      <c r="U2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="V2" s="0" t="s">
+      <c r="V2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="W2" s="0" t="s">
+      <c r="W2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="X2" s="0" t="s">
+      <c r="X2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="Y2" s="0" t="s">
+      <c r="Y2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="Z2" s="0" t="s">
+      <c r="Z2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AA2" s="0" t="s">
+      <c r="AA2" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="I3" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J3" s="0" t="s">
+      <c r="J3" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="K3" s="0" t="s">
+      <c r="K3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="L3" s="0" t="s">
+      <c r="L3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="M3" s="0" t="s">
+      <c r="M3" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="N3" s="0" t="s">
+      <c r="N3" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="O3" s="0" t="s">
+      <c r="O3" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="P3" s="0" t="s">
+      <c r="P3" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="Q3" s="0" t="s">
+      <c r="Q3" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="R3" s="0" t="s">
+      <c r="R3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="S3" s="0" t="s">
+      <c r="S3" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="T3" s="0" t="s">
+      <c r="T3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="U3" s="0" t="s">
+      <c r="U3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="V3" s="0" t="s">
+      <c r="V3" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="W3" s="0" t="s">
+      <c r="W3" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="X3" s="0" t="s">
+      <c r="X3" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="Y3" s="0" t="s">
+      <c r="Y3" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="Z3" s="0" t="s">
+      <c r="Z3" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AA3" s="0" t="s">
+      <c r="AA3" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="H4" s="0" t="s">
+      <c r="H4" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="I4" s="0" t="s">
+      <c r="I4" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="J4" s="0" t="s">
+      <c r="J4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="K4" s="0" t="s">
+      <c r="K4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L4" s="0" t="s">
+      <c r="L4" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="M4" s="0" t="s">
+      <c r="M4" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="N4" s="0" t="s">
+      <c r="N4" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="O4" s="0" t="s">
+      <c r="O4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="P4" s="0" t="s">
+      <c r="P4" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="Q4" s="0" t="s">
+      <c r="Q4" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="R4" s="0" t="s">
+      <c r="R4" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="S4" s="0" t="s">
+      <c r="S4" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="T4" s="0" t="s">
+      <c r="T4" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="U4" s="0" t="s">
+      <c r="U4" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="V4" s="0" t="s">
+      <c r="V4" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="W4" s="0" t="s">
+      <c r="W4" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="X4" s="0" t="s">
+      <c r="X4" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="Y4" s="0" t="s">
+      <c r="Y4" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Z4" s="0" t="s">
+      <c r="Z4" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="AA4" s="0" t="s">
+      <c r="AA4" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="H5" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="I5" s="0" t="s">
+      <c r="I5" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="J5" s="0" t="s">
+      <c r="J5" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="K5" s="0" t="s">
+      <c r="K5" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L5" s="0" t="s">
+      <c r="L5" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="M5" s="0" t="s">
+      <c r="M5" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="N5" s="0" t="s">
+      <c r="N5" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="O5" s="0" t="s">
+      <c r="O5" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="P5" s="0" t="s">
+      <c r="P5" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="Q5" s="0" t="s">
+      <c r="Q5" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="R5" s="0" t="s">
+      <c r="R5" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="S5" s="0" t="s">
+      <c r="S5" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="T5" s="0" t="s">
+      <c r="T5" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="U5" s="0" t="s">
+      <c r="U5" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="V5" s="0" t="s">
+      <c r="V5" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="W5" s="0" t="s">
+      <c r="W5" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="X5" s="0" t="s">
+      <c r="X5" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Y5" s="0" t="s">
+      <c r="Y5" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="Z5" s="0" t="s">
+      <c r="Z5" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="AA5" s="0" t="s">
+      <c r="AA5" s="1" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="H6" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="I6" s="0" t="s">
+      <c r="I6" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="J6" s="0" t="s">
+      <c r="J6" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="K6" s="0" t="s">
+      <c r="K6" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="L6" s="0" t="s">
+      <c r="L6" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="M6" s="0" t="s">
+      <c r="M6" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="N6" s="0" t="s">
+      <c r="N6" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="O6" s="0" t="s">
+      <c r="O6" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="P6" s="0" t="s">
+      <c r="P6" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="Q6" s="0" t="s">
+      <c r="Q6" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="R6" s="0" t="s">
+      <c r="R6" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="S6" s="0" t="s">
+      <c r="S6" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="T6" s="0" t="s">
+      <c r="T6" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="U6" s="0" t="s">
+      <c r="U6" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="V6" s="0" t="s">
+      <c r="V6" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="W6" s="0" t="s">
+      <c r="W6" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="X6" s="0" t="s">
+      <c r="X6" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="Y6" s="0" t="s">
+      <c r="Y6" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="Z6" s="0" t="s">
+      <c r="Z6" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="AA6" s="0" t="s">
+      <c r="AA6" s="1" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="H7" s="0" t="s">
+      <c r="H7" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I7" s="0" t="s">
+      <c r="I7" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="J7" s="0" t="s">
+      <c r="J7" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="K7" s="0" t="s">
+      <c r="K7" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L7" s="0" t="s">
+      <c r="L7" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="M7" s="0" t="s">
+      <c r="M7" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="N7" s="0" t="s">
+      <c r="N7" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="O7" s="0" t="s">
+      <c r="O7" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="P7" s="0" t="s">
+      <c r="P7" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="Q7" s="0" t="s">
+      <c r="Q7" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="R7" s="0" t="s">
+      <c r="R7" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="S7" s="0" t="s">
+      <c r="S7" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="T7" s="0" t="s">
+      <c r="T7" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="U7" s="0" t="s">
+      <c r="U7" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="V7" s="0" t="s">
+      <c r="V7" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="W7" s="0" t="s">
+      <c r="W7" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="X7" s="0" t="s">
+      <c r="X7" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="Y7" s="0" t="s">
+      <c r="Y7" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="Z7" s="0" t="s">
+      <c r="Z7" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="AA7" s="0" t="s">
+      <c r="AA7" s="1" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="H8" s="0" t="s">
+      <c r="H8" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="I8" s="0" t="s">
+      <c r="I8" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="J8" s="0" t="s">
+      <c r="J8" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="K8" s="0" t="s">
+      <c r="K8" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="L8" s="0" t="s">
+      <c r="L8" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="M8" s="0" t="s">
+      <c r="M8" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="N8" s="0" t="s">
+      <c r="N8" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="O8" s="0" t="s">
+      <c r="O8" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="P8" s="0" t="s">
+      <c r="P8" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="Q8" s="0" t="s">
+      <c r="Q8" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="R8" s="0" t="s">
+      <c r="R8" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="S8" s="0" t="s">
+      <c r="S8" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="T8" s="0" t="s">
+      <c r="T8" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="U8" s="0" t="s">
+      <c r="U8" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="V8" s="0" t="s">
+      <c r="V8" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="W8" s="0" t="s">
+      <c r="W8" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="X8" s="0" t="s">
+      <c r="X8" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="Y8" s="0" t="s">
+      <c r="Y8" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="Z8" s="0" t="s">
+      <c r="Z8" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="AA8" s="0" t="s">
+      <c r="AA8" s="1" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="H9" s="0" t="s">
+      <c r="H9" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I9" s="0" t="s">
+      <c r="I9" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="J9" s="0" t="s">
+      <c r="J9" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="K9" s="0" t="s">
+      <c r="K9" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="L9" s="0" t="s">
+      <c r="L9" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="M9" s="0" t="s">
+      <c r="M9" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="N9" s="0" t="s">
+      <c r="N9" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="O9" s="0" t="s">
+      <c r="O9" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="P9" s="0" t="s">
+      <c r="P9" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="Q9" s="0" t="s">
+      <c r="Q9" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="R9" s="0" t="s">
+      <c r="R9" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="S9" s="0" t="s">
+      <c r="S9" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="T9" s="0" t="s">
+      <c r="T9" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="U9" s="0" t="s">
+      <c r="U9" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="V9" s="0" t="s">
+      <c r="V9" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="W9" s="0" t="s">
+      <c r="W9" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="X9" s="0" t="s">
+      <c r="X9" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="Y9" s="0" t="s">
+      <c r="Y9" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="Z9" s="0" t="s">
+      <c r="Z9" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="AA9" s="0" t="s">
+      <c r="AA9" s="1" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="G10" s="0" t="s">
+      <c r="G10" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="H10" s="0" t="s">
+      <c r="H10" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="I10" s="0" t="s">
+      <c r="I10" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="J10" s="0" t="s">
+      <c r="J10" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="K10" s="0" t="s">
+      <c r="K10" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="L10" s="0" t="s">
+      <c r="L10" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="M10" s="0" t="s">
+      <c r="M10" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="N10" s="0" t="s">
+      <c r="N10" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="O10" s="0" t="s">
+      <c r="O10" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="P10" s="0" t="s">
+      <c r="P10" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="Q10" s="0" t="s">
+      <c r="Q10" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="R10" s="0" t="s">
+      <c r="R10" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="S10" s="0" t="s">
+      <c r="S10" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="T10" s="0" t="s">
+      <c r="T10" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="U10" s="0" t="s">
+      <c r="U10" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="V10" s="0" t="s">
+      <c r="V10" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="W10" s="0" t="s">
+      <c r="W10" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="X10" s="0" t="s">
+      <c r="X10" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="Y10" s="0" t="s">
+      <c r="Y10" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="Z10" s="0" t="s">
+      <c r="Z10" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="AA10" s="0" t="s">
+      <c r="AA10" s="1" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="G11" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="H11" s="0" t="s">
+      <c r="H11" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="I11" s="0" t="s">
+      <c r="I11" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="J11" s="0" t="s">
+      <c r="J11" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="K11" s="0" t="s">
+      <c r="K11" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="L11" s="0" t="s">
+      <c r="L11" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="M11" s="0" t="s">
+      <c r="M11" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="N11" s="0" t="s">
+      <c r="N11" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="O11" s="0" t="s">
+      <c r="O11" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="P11" s="0" t="s">
+      <c r="P11" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="Q11" s="0" t="s">
+      <c r="Q11" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="R11" s="0" t="s">
+      <c r="R11" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="S11" s="0" t="s">
+      <c r="S11" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="T11" s="0" t="s">
+      <c r="T11" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="U11" s="0" t="s">
+      <c r="U11" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="V11" s="0" t="s">
+      <c r="V11" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="W11" s="0" t="s">
+      <c r="W11" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="X11" s="0" t="s">
+      <c r="X11" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="Y11" s="0" t="s">
+      <c r="Y11" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="Z11" s="0" t="s">
+      <c r="Z11" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA11" s="0" t="s">
+      <c r="AA11" s="1" t="s">
         <v>276</v>
       </c>
     </row>
